--- a/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/OLS_vs_RF_Comparison.xlsx
+++ b/Mini-Project/Agricultural Machinery Inventory from ABEMIS/Regression Parameters Output V3/OLS_vs_RF_Comparison.xlsx
@@ -455,13 +455,13 @@
         <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9111462395227746</v>
+        <v>0.9156740904867036</v>
       </c>
       <c r="D2" t="n">
-        <v>1.090164544085301</v>
+        <v>0.9503597492453506</v>
       </c>
       <c r="E2" t="n">
-        <v>1.610165723791116</v>
+        <v>1.53425010525932</v>
       </c>
     </row>
     <row r="3">
@@ -474,13 +474,13 @@
         <v>76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.761061258210871</v>
+        <v>0.7038782249734605</v>
       </c>
       <c r="D3" t="n">
-        <v>1.682584321834272</v>
+        <v>1.881717027092503</v>
       </c>
       <c r="E3" t="n">
-        <v>2.640437896320794</v>
+        <v>2.875085846522413</v>
       </c>
     </row>
     <row r="4">
@@ -493,13 +493,13 @@
         <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7222630958664233</v>
+        <v>0.7031747562412759</v>
       </c>
       <c r="D4" t="n">
-        <v>1.872316663693625</v>
+        <v>1.878885328210188</v>
       </c>
       <c r="E4" t="n">
-        <v>2.846750896766141</v>
+        <v>2.878498856650352</v>
       </c>
     </row>
   </sheetData>
@@ -561,7 +561,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.22</v>
+        <v>8.48</v>
       </c>
       <c r="D2" t="n">
-        <v>2.24</v>
+        <v>9.15</v>
       </c>
       <c r="E2" t="n">
-        <v>1.589712946590448</v>
+        <v>3.592270449735453</v>
       </c>
       <c r="F2" t="n">
-        <v>2.444279088592875</v>
+        <v>3.203909542141191</v>
       </c>
       <c r="G2" t="n">
-        <v>1.671812651303803</v>
+        <v>3.114701695693136</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -593,28 +593,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>62.98</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="E3" t="n">
-        <v>5.550206095478606</v>
+        <v>10.33916534391532</v>
       </c>
       <c r="F3" t="n">
-        <v>1.437391088004509</v>
+        <v>16.48941848781758</v>
       </c>
       <c r="G3" t="n">
-        <v>2.033818882122193</v>
+        <v>17.63324451312414</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -625,135 +625,135 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Combine Harvester</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Harvest Machinery</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>7.5</v>
       </c>
       <c r="D4" t="n">
-        <v>12.1</v>
+        <v>1.01</v>
       </c>
       <c r="E4" t="n">
-        <v>14.83314730158731</v>
+        <v>3.914962510822512</v>
       </c>
       <c r="F4" t="n">
-        <v>17.42352759023686</v>
+        <v>2.965014151925358</v>
       </c>
       <c r="G4" t="n">
-        <v>18.69925424648229</v>
+        <v>2.965014151925359</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>GLOBAL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hand Tractor</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.12</v>
+        <v>6.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.65</v>
+        <v>3.46</v>
       </c>
       <c r="E5" t="n">
-        <v>1.922985945165945</v>
+        <v>3.447227539682541</v>
       </c>
       <c r="F5" t="n">
-        <v>2.420419183365663</v>
+        <v>2.623735023045597</v>
       </c>
       <c r="G5" t="n">
-        <v>5.683714141336993</v>
+        <v>2.769061510974542</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hand Tractor</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.89</v>
+        <v>8.56</v>
       </c>
       <c r="D6" t="n">
-        <v>1.87</v>
+        <v>4.13</v>
       </c>
       <c r="E6" t="n">
-        <v>1.702475892255892</v>
+        <v>4.69954681697932</v>
       </c>
       <c r="F6" t="n">
-        <v>2.365541401343074</v>
+        <v>3.223411206648606</v>
       </c>
       <c r="G6" t="n">
-        <v>5.63802763492251</v>
+        <v>3.126319853162668</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Sheller</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.22</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="E7" t="n">
-        <v>1.759485185185185</v>
+        <v>2.169151651034151</v>
       </c>
       <c r="F7" t="n">
-        <v>2.444279088592875</v>
+        <v>3.32091952918568</v>
       </c>
       <c r="G7" t="n">
-        <v>2.637672642192483</v>
+        <v>2.063462166928279</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Walking-Type Agricultural Tractor</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -762,51 +762,51 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.22</v>
+        <v>49.4</v>
       </c>
       <c r="D8" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="E8" t="n">
-        <v>9.050791944444395</v>
+        <v>15.72545809644059</v>
       </c>
       <c r="F8" t="n">
-        <v>2.444279088592875</v>
+        <v>13.17901093768391</v>
       </c>
       <c r="G8" t="n">
-        <v>5.703577839778073</v>
+        <v>14.6420170817718</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.59</v>
+        <v>0.63</v>
       </c>
       <c r="E9" t="n">
-        <v>2.151842359307359</v>
+        <v>1.176639416786918</v>
       </c>
       <c r="F9" t="n">
-        <v>3.393903316635932</v>
+        <v>1.892422604017539</v>
       </c>
       <c r="G9" t="n">
-        <v>2.203179980532048</v>
+        <v>1.300446376365057</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Seeder</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -826,83 +826,83 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>70</v>
+        <v>76.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10.1</v>
+        <v>25.3</v>
       </c>
       <c r="E10" t="n">
-        <v>12.21094519841269</v>
+        <v>23.95878297258297</v>
       </c>
       <c r="F10" t="n">
-        <v>17.90072569478111</v>
+        <v>19.73644562830216</v>
       </c>
       <c r="G10" t="n">
-        <v>18.57128168990952</v>
+        <v>20.56720249439168</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Seeder</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.7</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>1.04</v>
+        <v>10.1</v>
       </c>
       <c r="E11" t="n">
-        <v>1.898265805675809</v>
+        <v>11.47594249398747</v>
       </c>
       <c r="F11" t="n">
-        <v>3.036004738227744</v>
+        <v>18.20068954834325</v>
       </c>
       <c r="G11" t="n">
-        <v>2.262103867575701</v>
+        <v>18.64654269870798</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.48</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>9.15</v>
+        <v>22.5</v>
       </c>
       <c r="E12" t="n">
-        <v>4.24408261904762</v>
+        <v>23.7369797979798</v>
       </c>
       <c r="F12" t="n">
-        <v>3.222111999000002</v>
+        <v>21.8816287241178</v>
       </c>
       <c r="G12" t="n">
-        <v>3.104156826512186</v>
+        <v>22.50555311264651</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -913,32 +913,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Seeder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.22</v>
+        <v>40.4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.12</v>
+        <v>10.1</v>
       </c>
       <c r="E13" t="n">
-        <v>1.450188241110742</v>
+        <v>9.640259907407399</v>
       </c>
       <c r="F13" t="n">
-        <v>2.444279088592875</v>
+        <v>10.98507368059973</v>
       </c>
       <c r="G13" t="n">
-        <v>1.671812651303803</v>
+        <v>12.53574387807767</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
@@ -960,13 +960,13 @@
         <v>1.62</v>
       </c>
       <c r="E14" t="n">
-        <v>1.837548237133236</v>
+        <v>1.964635607263106</v>
       </c>
       <c r="F14" t="n">
-        <v>3.39151732611321</v>
+        <v>3.376986814644498</v>
       </c>
       <c r="G14" t="n">
-        <v>2.201240405076969</v>
+        <v>2.142323436580488</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -977,60 +977,60 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sheller</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.960000000000001</v>
+        <v>63.52</v>
       </c>
       <c r="D15" t="n">
-        <v>1.72</v>
+        <v>9.1</v>
       </c>
       <c r="E15" t="n">
-        <v>2.315880565175565</v>
+        <v>10.34722089947088</v>
       </c>
       <c r="F15" t="n">
-        <v>3.336639544090621</v>
+        <v>16.62105472324264</v>
       </c>
       <c r="G15" t="n">
-        <v>2.090198844323896</v>
+        <v>17.75218875560796</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>63.52</v>
+        <v>7.3</v>
       </c>
       <c r="D16" t="n">
-        <v>9.1</v>
+        <v>2.17</v>
       </c>
       <c r="E16" t="n">
-        <v>10.08835493025492</v>
+        <v>2.287470573593072</v>
       </c>
       <c r="F16" t="n">
-        <v>16.35460383605774</v>
+        <v>2.916259990656821</v>
       </c>
       <c r="G16" t="n">
-        <v>17.71541846656796</v>
+        <v>2.108151270558575</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1041,60 +1041,60 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Combine Harvester</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Harvest Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1</v>
+        <v>1.26</v>
       </c>
       <c r="E17" t="n">
-        <v>8.062742510822487</v>
+        <v>1.147206957671958</v>
       </c>
       <c r="F17" t="n">
-        <v>3.537062747999206</v>
+        <v>2.136193410360225</v>
       </c>
       <c r="G17" t="n">
-        <v>3.537062747999206</v>
+        <v>1.492757065458751</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.65</v>
+        <v>33.6</v>
       </c>
       <c r="D18" t="n">
-        <v>3.26</v>
+        <v>10.1</v>
       </c>
       <c r="E18" t="n">
-        <v>3.504752225274725</v>
+        <v>10.00478754689754</v>
       </c>
       <c r="F18" t="n">
-        <v>2.785475733342014</v>
+        <v>9.327432197469468</v>
       </c>
       <c r="G18" t="n">
-        <v>2.842296072737629</v>
+        <v>11.16179665354154</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1105,28 +1105,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sheller</t>
+          <t>Hand Tractor</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.210000000000001</v>
+        <v>5.22</v>
       </c>
       <c r="D19" t="n">
-        <v>2.44</v>
+        <v>1.41</v>
       </c>
       <c r="E19" t="n">
-        <v>2.234771305916304</v>
+        <v>1.49181038961039</v>
       </c>
       <c r="F19" t="n">
-        <v>3.157690254886528</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G19" t="n">
-        <v>1.958913706712928</v>
+        <v>5.272976901396118</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,64 +1137,64 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Seeder</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40.4</v>
+        <v>4.17</v>
       </c>
       <c r="D20" t="n">
-        <v>10.1</v>
+        <v>2.05</v>
       </c>
       <c r="E20" t="n">
-        <v>9.260824100529089</v>
+        <v>2.448274422799422</v>
       </c>
       <c r="F20" t="n">
-        <v>10.83819374752622</v>
+        <v>2.153257366804213</v>
       </c>
       <c r="G20" t="n">
-        <v>12.69162695134992</v>
+        <v>2.488773462022069</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Combine Harvester</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Harvest Machinery</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11.9</v>
+        <v>62</v>
       </c>
       <c r="D21" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="E21" t="n">
-        <v>4.073140752765755</v>
+        <v>13.85569450937951</v>
       </c>
       <c r="F21" t="n">
-        <v>4.038120757770668</v>
+        <v>16.25052309760175</v>
       </c>
       <c r="G21" t="n">
-        <v>2.726865353403306</v>
+        <v>16.25052309760175</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>GLOBAL</t>
         </is>
       </c>
     </row>
@@ -1216,13 +1216,13 @@
         <v>1.35</v>
       </c>
       <c r="E22" t="n">
-        <v>1.404248373015872</v>
+        <v>1.398510482202983</v>
       </c>
       <c r="F22" t="n">
-        <v>2.444279088592875</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G22" t="n">
-        <v>5.703577839778073</v>
+        <v>5.272976901396118</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,13 +1248,13 @@
         <v>3.59</v>
       </c>
       <c r="E23" t="n">
-        <v>2.676362099567098</v>
+        <v>2.62977704184704</v>
       </c>
       <c r="F23" t="n">
-        <v>2.978740965682435</v>
+        <v>2.955263319671651</v>
       </c>
       <c r="G23" t="n">
-        <v>2.958201652277188</v>
+        <v>2.966570187956596</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.46</v>
+        <v>1.3</v>
       </c>
       <c r="D24" t="n">
-        <v>5.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.111659973544975</v>
+        <v>1.59185244107744</v>
       </c>
       <c r="F24" t="n">
-        <v>2.978740965682435</v>
+        <v>1.453635152600704</v>
       </c>
       <c r="G24" t="n">
-        <v>2.958201652277188</v>
+        <v>2.071972062802589</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         <v>1.88</v>
       </c>
       <c r="E25" t="n">
-        <v>1.523347182539683</v>
+        <v>1.500083783068783</v>
       </c>
       <c r="F25" t="n">
-        <v>2.444279088592875</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G25" t="n">
-        <v>2.637672642192483</v>
+        <v>2.641261778809684</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1329,28 +1329,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>11.9</v>
+        <v>4.75</v>
       </c>
       <c r="D26" t="n">
-        <v>4.65</v>
+        <v>1.74</v>
       </c>
       <c r="E26" t="n">
-        <v>4.073140752765755</v>
+        <v>2.167038522126023</v>
       </c>
       <c r="F26" t="n">
-        <v>4.038120757770668</v>
+        <v>2.294644434482971</v>
       </c>
       <c r="G26" t="n">
-        <v>2.726865353403306</v>
+        <v>2.57300510367618</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Thresher</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.8</v>
+        <v>11.94</v>
       </c>
       <c r="D27" t="n">
-        <v>3.46</v>
+        <v>3.99</v>
       </c>
       <c r="E27" t="n">
-        <v>2.782781453823953</v>
+        <v>3.888647647907647</v>
       </c>
       <c r="F27" t="n">
-        <v>2.582666538910708</v>
+        <v>4.047356532086885</v>
       </c>
       <c r="G27" t="n">
-        <v>2.72066676087513</v>
+        <v>2.617768788050697</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1408,13 +1408,13 @@
         <v>1.54</v>
       </c>
       <c r="E28" t="n">
-        <v>1.094937065897066</v>
+        <v>1.064450501443002</v>
       </c>
       <c r="F28" t="n">
-        <v>2.081608529139246</v>
+        <v>2.038685087823151</v>
       </c>
       <c r="G28" t="n">
-        <v>1.310021260685543</v>
+        <v>1.415832789821273</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Seeder</t>
+          <t>Walking-Type Agricultural Tractor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1434,19 +1434,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37.6</v>
+        <v>10.3</v>
       </c>
       <c r="D29" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
       <c r="E29" t="n">
-        <v>9.219275767195755</v>
+        <v>9.057155476190438</v>
       </c>
       <c r="F29" t="n">
-        <v>10.17011640116427</v>
+        <v>3.64757240968488</v>
       </c>
       <c r="G29" t="n">
-        <v>12.13544339499969</v>
+        <v>6.321722104396184</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1472,13 +1472,13 @@
         <v>3.18</v>
       </c>
       <c r="E30" t="n">
-        <v>3.610884571909571</v>
+        <v>3.311150798460801</v>
       </c>
       <c r="F30" t="n">
-        <v>4.038120757770668</v>
+        <v>4.037605699833177</v>
       </c>
       <c r="G30" t="n">
-        <v>2.726865353403306</v>
+        <v>2.61085321930204</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1498,19 +1498,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.31</v>
+        <v>17.23</v>
       </c>
       <c r="D31" t="n">
-        <v>2.99</v>
+        <v>7.91</v>
       </c>
       <c r="E31" t="n">
-        <v>4.246050954785958</v>
+        <v>3.464777423039924</v>
       </c>
       <c r="F31" t="n">
-        <v>2.942951107841616</v>
+        <v>5.336904097639695</v>
       </c>
       <c r="G31" t="n">
-        <v>2.936737656066158</v>
+        <v>4.385437668923259</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1521,28 +1521,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>22.4</v>
+        <v>7.46</v>
       </c>
       <c r="D32" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="E32" t="n">
-        <v>8.742334682539688</v>
+        <v>2.301065386002883</v>
       </c>
       <c r="F32" t="n">
-        <v>6.543410806627977</v>
+        <v>2.955263319671651</v>
       </c>
       <c r="G32" t="n">
-        <v>8.685211486639918</v>
+        <v>2.138920980813566</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1562,19 +1562,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.46</v>
+        <v>6.3</v>
       </c>
       <c r="D33" t="n">
-        <v>2.28</v>
+        <v>1.09</v>
       </c>
       <c r="E33" t="n">
-        <v>2.676362099567098</v>
+        <v>1.738686216504084</v>
       </c>
       <c r="F33" t="n">
-        <v>2.978740965682435</v>
+        <v>2.672489184314135</v>
       </c>
       <c r="G33" t="n">
-        <v>2.958201652277188</v>
+        <v>1.91584058146488</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1585,28 +1585,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Thresher</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.56</v>
+        <v>11.9</v>
       </c>
       <c r="D34" t="n">
-        <v>2.1</v>
+        <v>4.25</v>
       </c>
       <c r="E34" t="n">
-        <v>1.711668888888889</v>
+        <v>3.888647647907647</v>
       </c>
       <c r="F34" t="n">
-        <v>2.048204661821148</v>
+        <v>4.037605699833177</v>
       </c>
       <c r="G34" t="n">
-        <v>2.400137750790426</v>
+        <v>2.61085321930204</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1632,13 +1632,13 @@
         <v>0.58</v>
       </c>
       <c r="E35" t="n">
-        <v>1.80544443963444</v>
+        <v>1.782254557479558</v>
       </c>
       <c r="F35" t="n">
-        <v>2.623228377796969</v>
+        <v>2.592044818221048</v>
       </c>
       <c r="G35" t="n">
-        <v>2.74499262324763</v>
+        <v>2.750182005086552</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1649,28 +1649,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.960000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>2.15</v>
+        <v>28</v>
       </c>
       <c r="E36" t="n">
-        <v>2.022963152958153</v>
+        <v>24.74713760221261</v>
       </c>
       <c r="F36" t="n">
-        <v>3.336639544090621</v>
+        <v>21.15031630508975</v>
       </c>
       <c r="G36" t="n">
-        <v>2.156630169610159</v>
+        <v>21.84475176551418</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1696,13 +1696,13 @@
         <v>2.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1.363555513468013</v>
+        <v>1.329980904280905</v>
       </c>
       <c r="F37" t="n">
-        <v>2.041046690252984</v>
+        <v>1.997244050744894</v>
       </c>
       <c r="G37" t="n">
-        <v>1.139694448020485</v>
+        <v>1.144310067868497</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1728,13 +1728,13 @@
         <v>1.49</v>
       </c>
       <c r="E38" t="n">
-        <v>2.010180886243385</v>
+        <v>2.124282248677248</v>
       </c>
       <c r="F38" t="n">
-        <v>3.393903316635932</v>
+        <v>3.379424522707925</v>
       </c>
       <c r="G38" t="n">
-        <v>3.207184008325127</v>
+        <v>3.219265112918928</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1754,19 +1754,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9.17</v>
+        <v>3.97</v>
       </c>
       <c r="D39" t="n">
-        <v>5.24</v>
+        <v>1.61</v>
       </c>
       <c r="E39" t="n">
-        <v>3.74585761904762</v>
+        <v>1.064006574074075</v>
       </c>
       <c r="F39" t="n">
-        <v>3.386745345067768</v>
+        <v>2.104503205535676</v>
       </c>
       <c r="G39" t="n">
-        <v>3.202891209082921</v>
+        <v>1.467756675876571</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1777,28 +1777,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>7.46</v>
       </c>
       <c r="D40" t="n">
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="E40" t="n">
-        <v>2.044210597643097</v>
+        <v>1.806977870555369</v>
       </c>
       <c r="F40" t="n">
-        <v>2.978740965682435</v>
+        <v>2.955263319671651</v>
       </c>
       <c r="G40" t="n">
-        <v>1.865693851348349</v>
+        <v>2.138920980813566</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1809,28 +1809,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>19.9</v>
+        <v>2.87</v>
       </c>
       <c r="D41" t="n">
-        <v>7.48</v>
+        <v>1.75</v>
       </c>
       <c r="E41" t="n">
-        <v>6.321415555555554</v>
+        <v>2.343637447089946</v>
       </c>
       <c r="F41" t="n">
-        <v>5.946913175947665</v>
+        <v>1.836355318558721</v>
       </c>
       <c r="G41" t="n">
-        <v>8.136195984455577</v>
+        <v>2.299978403142165</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1850,19 +1850,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.46</v>
+        <v>8.82</v>
       </c>
       <c r="D42" t="n">
-        <v>4.42</v>
+        <v>1.97</v>
       </c>
       <c r="E42" t="n">
-        <v>2.111659973544975</v>
+        <v>1.975936002886003</v>
       </c>
       <c r="F42" t="n">
-        <v>2.978740965682435</v>
+        <v>3.286791616297704</v>
       </c>
       <c r="G42" t="n">
-        <v>2.958201652277188</v>
+        <v>2.40046351798099</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         <v>1.49</v>
       </c>
       <c r="E43" t="n">
-        <v>1.245543742183742</v>
+        <v>1.131082374939875</v>
       </c>
       <c r="F43" t="n">
-        <v>2.088766500707409</v>
+        <v>2.045998212013431</v>
       </c>
       <c r="G43" t="n">
-        <v>1.31716188023722</v>
+        <v>1.421602110494084</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1905,28 +1905,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>11.9</v>
+        <v>3.12</v>
       </c>
       <c r="D44" t="n">
-        <v>1.47</v>
+        <v>2.56</v>
       </c>
       <c r="E44" t="n">
-        <v>3.610884571909571</v>
+        <v>2.403676759259259</v>
       </c>
       <c r="F44" t="n">
-        <v>4.038120757770668</v>
+        <v>1.897298020144393</v>
       </c>
       <c r="G44" t="n">
-        <v>2.726865353403306</v>
+        <v>2.336285145234454</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1946,19 +1946,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.69</v>
+        <v>4.1</v>
       </c>
       <c r="D45" t="n">
-        <v>2.75</v>
+        <v>1.69</v>
       </c>
       <c r="E45" t="n">
-        <v>2.151781865079367</v>
+        <v>1.29416414021164</v>
       </c>
       <c r="F45" t="n">
-        <v>2.317821590888649</v>
+        <v>2.136193410360225</v>
       </c>
       <c r="G45" t="n">
-        <v>2.561833188913514</v>
+        <v>1.492757065458751</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1969,39 +1969,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Mechanical Dryer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>60.6</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>2.5</v>
       </c>
       <c r="E46" t="n">
-        <v>20.26365303030303</v>
+        <v>1.485404001924002</v>
       </c>
       <c r="F46" t="n">
-        <v>15.65789460342314</v>
+        <v>3.32091952918568</v>
       </c>
       <c r="G46" t="n">
-        <v>17.07416836001665</v>
+        <v>2.063462166928279</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Walking-Type Agricultural Tractor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2010,23 +2010,23 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>76.3</v>
+        <v>5.22</v>
       </c>
       <c r="D47" t="n">
-        <v>25.3</v>
+        <v>9.1</v>
       </c>
       <c r="E47" t="n">
-        <v>23.43143624338623</v>
+        <v>9.001377777777728</v>
       </c>
       <c r="F47" t="n">
-        <v>19.4038997240955</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G47" t="n">
-        <v>20.52198571373431</v>
+        <v>5.272976901396118</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
@@ -2048,13 +2048,13 @@
         <v>1.66</v>
       </c>
       <c r="E48" t="n">
-        <v>3.610884571909571</v>
+        <v>3.311150798460801</v>
       </c>
       <c r="F48" t="n">
-        <v>4.038120757770668</v>
+        <v>4.037605699833177</v>
       </c>
       <c r="G48" t="n">
-        <v>2.726865353403306</v>
+        <v>2.61085321930204</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2074,19 +2074,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.22</v>
+        <v>4.89</v>
       </c>
       <c r="D49" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="E49" t="n">
-        <v>1.478863716931216</v>
+        <v>1.554997757335257</v>
       </c>
       <c r="F49" t="n">
-        <v>2.444279088592875</v>
+        <v>2.328772347370947</v>
       </c>
       <c r="G49" t="n">
-        <v>5.703577839778073</v>
+        <v>5.204849752382334</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Hand Tractor</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2106,55 +2106,55 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>67.2</v>
+        <v>5.22</v>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>1.62</v>
       </c>
       <c r="E50" t="n">
-        <v>13.11792719576718</v>
+        <v>1.49181038961039</v>
       </c>
       <c r="F50" t="n">
-        <v>17.23264834841916</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G50" t="n">
-        <v>18.52356928578331</v>
+        <v>5.272976901396118</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Sheller</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.1</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>0.63</v>
+        <v>2.96</v>
       </c>
       <c r="E51" t="n">
-        <v>1.186744737854738</v>
+        <v>2.169151651034151</v>
       </c>
       <c r="F51" t="n">
-        <v>1.938449097775971</v>
+        <v>3.32091952918568</v>
       </c>
       <c r="G51" t="n">
-        <v>1.16720886965202</v>
+        <v>2.063462166928279</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
@@ -2170,19 +2170,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.44</v>
+        <v>7.69</v>
       </c>
       <c r="D52" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="E52" t="n">
-        <v>2.676362099567098</v>
+        <v>4.268847777777779</v>
       </c>
       <c r="F52" t="n">
-        <v>2.973968984636992</v>
+        <v>3.011330605130469</v>
       </c>
       <c r="G52" t="n">
-        <v>2.955339786115717</v>
+        <v>2.999972390681502</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2202,19 +2202,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6.9</v>
+        <v>3.57</v>
       </c>
       <c r="D53" t="n">
-        <v>3.63</v>
+        <v>1.82</v>
       </c>
       <c r="E53" t="n">
-        <v>3.573573283475785</v>
+        <v>1.898106280663781</v>
       </c>
       <c r="F53" t="n">
-        <v>2.845125496410045</v>
+        <v>2.006994882998602</v>
       </c>
       <c r="G53" t="n">
-        <v>2.878069399756011</v>
+        <v>2.401637281000575</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2225,28 +2225,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>75.59999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="D54" t="n">
-        <v>28.5</v>
+        <v>4.68</v>
       </c>
       <c r="E54" t="n">
-        <v>24.81999178691677</v>
+        <v>5.278808915343919</v>
       </c>
       <c r="F54" t="n">
-        <v>19.23688038750501</v>
+        <v>2.184947571628762</v>
       </c>
       <c r="G54" t="n">
-        <v>20.36826137312269</v>
+        <v>2.50765296791006</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7.3</v>
+        <v>5.1</v>
       </c>
       <c r="D55" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="E55" t="n">
-        <v>2.49575868746994</v>
+        <v>1.754740753968255</v>
       </c>
       <c r="F55" t="n">
-        <v>2.940565117318894</v>
+        <v>2.379964216702911</v>
       </c>
       <c r="G55" t="n">
-        <v>2.166895606886685</v>
+        <v>2.623834542605385</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2298,19 +2298,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5.1</v>
+        <v>5.97</v>
       </c>
       <c r="D56" t="n">
-        <v>2.18</v>
+        <v>1.41</v>
       </c>
       <c r="E56" t="n">
-        <v>1.886966587764087</v>
+        <v>1.74858850181137</v>
       </c>
       <c r="F56" t="n">
-        <v>2.41564720232022</v>
+        <v>2.592044818221048</v>
       </c>
       <c r="G56" t="n">
-        <v>2.62050144522366</v>
+        <v>1.85237805406396</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2330,19 +2330,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4.85</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D57" t="n">
-        <v>0.91</v>
+        <v>1.26</v>
       </c>
       <c r="E57" t="n">
-        <v>1.750718161838161</v>
+        <v>2.124282248677248</v>
       </c>
       <c r="F57" t="n">
-        <v>2.355997439252189</v>
+        <v>3.379424522707925</v>
       </c>
       <c r="G57" t="n">
-        <v>2.584728118205278</v>
+        <v>3.219265112918928</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2362,19 +2362,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9.199999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>1.26</v>
+        <v>4.66</v>
       </c>
       <c r="E58" t="n">
-        <v>2.010180886243385</v>
+        <v>3.595104338624341</v>
       </c>
       <c r="F58" t="n">
-        <v>3.393903316635932</v>
+        <v>3.174657045380068</v>
       </c>
       <c r="G58" t="n">
-        <v>3.207184008325127</v>
+        <v>3.097274459488837</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2394,19 +2394,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6.07</v>
+        <v>5.22</v>
       </c>
       <c r="D59" t="n">
-        <v>2.57</v>
+        <v>0.82</v>
       </c>
       <c r="E59" t="n">
-        <v>3.214718362840861</v>
+        <v>1.763893063880563</v>
       </c>
       <c r="F59" t="n">
-        <v>2.647088283024181</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G59" t="n">
-        <v>2.759301954054983</v>
+        <v>1.708145037243689</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -2417,71 +2417,71 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Combine Harvester</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Harvest Machinery</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5.14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="E60" t="n">
-        <v>2.093057682040181</v>
+        <v>8.334308612313588</v>
       </c>
       <c r="F60" t="n">
-        <v>2.425191164411105</v>
+        <v>3.525687006513536</v>
       </c>
       <c r="G60" t="n">
-        <v>2.626225177546601</v>
+        <v>3.525687006513536</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>GLOBAL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sheller</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8.960000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="D61" t="n">
-        <v>2.96</v>
+        <v>2.53</v>
       </c>
       <c r="E61" t="n">
-        <v>2.315880565175565</v>
+        <v>1.898226243144111</v>
       </c>
       <c r="F61" t="n">
-        <v>3.336639544090621</v>
+        <v>2.660300643997001</v>
       </c>
       <c r="G61" t="n">
-        <v>2.090198844323896</v>
+        <v>1.906225047010195</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2490,19 +2490,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5.97</v>
+        <v>1.49</v>
       </c>
       <c r="D62" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="E62" t="n">
-        <v>1.475861188117438</v>
+        <v>1.483097282347282</v>
       </c>
       <c r="F62" t="n">
-        <v>2.623228377796969</v>
+        <v>1.499951605805814</v>
       </c>
       <c r="G62" t="n">
-        <v>1.850328140095708</v>
+        <v>2.099565186792729</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2513,32 +2513,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rice Transplanter</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="D63" t="n">
-        <v>0.8100000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="E63" t="n">
-        <v>2.230945525493026</v>
+        <v>5.463875544733046</v>
       </c>
       <c r="F63" t="n">
-        <v>1.819149571639909</v>
+        <v>1.390254742951606</v>
       </c>
       <c r="G63" t="n">
-        <v>5.183148940621784</v>
+        <v>2.034213051026608</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
@@ -2554,19 +2554,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8.31</v>
+        <v>4.38</v>
       </c>
       <c r="D64" t="n">
-        <v>3.42</v>
+        <v>2.38</v>
       </c>
       <c r="E64" t="n">
-        <v>4.268770965608466</v>
+        <v>2.227234012746512</v>
       </c>
       <c r="F64" t="n">
-        <v>3.181550160113741</v>
+        <v>2.204449236136178</v>
       </c>
       <c r="G64" t="n">
-        <v>3.079830964139687</v>
+        <v>2.519271125379592</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4.85</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D65" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="E65" t="n">
-        <v>1.454185542328041</v>
+        <v>2.291416005291005</v>
       </c>
       <c r="F65" t="n">
-        <v>2.355997439252189</v>
+        <v>3.501309925879267</v>
       </c>
       <c r="G65" t="n">
-        <v>1.583745010166464</v>
+        <v>3.291878597103507</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2609,28 +2609,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Four-Wheel Tractor</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8.82</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>1.97</v>
+        <v>12.1</v>
       </c>
       <c r="E66" t="n">
-        <v>2.172111988335737</v>
+        <v>10.78000764050762</v>
       </c>
       <c r="F66" t="n">
-        <v>3.303235676772524</v>
+        <v>17.49375420994945</v>
       </c>
       <c r="G66" t="n">
-        <v>2.528686997504946</v>
+        <v>18.54074502985254</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2641,39 +2641,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Sheller</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9.699999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="E67" t="n">
-        <v>2.260812592592593</v>
+        <v>2.267791860084359</v>
       </c>
       <c r="F67" t="n">
-        <v>3.513202842771993</v>
+        <v>3.32091952918568</v>
       </c>
       <c r="G67" t="n">
-        <v>3.278730662361891</v>
+        <v>2.063462166928279</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="D68" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="E68" t="n">
-        <v>1.945346357346358</v>
+        <v>3.450294206349207</v>
       </c>
       <c r="F68" t="n">
-        <v>2.690036112433163</v>
+        <v>2.611546482728463</v>
       </c>
       <c r="G68" t="n">
-        <v>1.916973922578019</v>
+        <v>2.761800162556084</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2705,28 +2705,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>30.5</v>
+        <v>4.85</v>
       </c>
       <c r="D69" t="n">
-        <v>10.3</v>
+        <v>1.41</v>
       </c>
       <c r="E69" t="n">
-        <v>9.608748654401159</v>
+        <v>1.780929669312169</v>
       </c>
       <c r="F69" t="n">
-        <v>8.476063130032188</v>
+        <v>2.31902151511724</v>
       </c>
       <c r="G69" t="n">
-        <v>10.46402171371718</v>
+        <v>2.587527800513096</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>17.23</v>
+        <v>5.97</v>
       </c>
       <c r="D70" t="n">
-        <v>7.91</v>
+        <v>1.45</v>
       </c>
       <c r="E70" t="n">
-        <v>3.395111891534392</v>
+        <v>1.74858850181137</v>
       </c>
       <c r="F70" t="n">
-        <v>5.309853706381093</v>
+        <v>2.592044818221048</v>
       </c>
       <c r="G70" t="n">
-        <v>4.356223272155561</v>
+        <v>1.85237805406396</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2769,28 +2769,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Thresher</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4.48</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="E71" t="n">
-        <v>2.09599873015873</v>
+        <v>1.767020593018094</v>
       </c>
       <c r="F71" t="n">
-        <v>2.267715789911503</v>
+        <v>3.32091952918568</v>
       </c>
       <c r="G71" t="n">
-        <v>2.531783594218073</v>
+        <v>2.102558916275707</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2810,19 +2810,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4.85</v>
+        <v>5.22</v>
       </c>
       <c r="D72" t="n">
-        <v>1.41</v>
+        <v>2.24</v>
       </c>
       <c r="E72" t="n">
-        <v>1.891756534854035</v>
+        <v>1.799720318292819</v>
       </c>
       <c r="F72" t="n">
-        <v>2.355997439252189</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G72" t="n">
-        <v>2.584728118205278</v>
+        <v>1.708145037243689</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -2833,28 +2833,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>85.09999999999999</v>
+        <v>4.69</v>
       </c>
       <c r="D73" t="n">
-        <v>22.5</v>
+        <v>2.75</v>
       </c>
       <c r="E73" t="n">
-        <v>24.16819563492062</v>
+        <v>2.207789051226553</v>
       </c>
       <c r="F73" t="n">
-        <v>21.50357138409019</v>
+        <v>2.28001818610241</v>
       </c>
       <c r="G73" t="n">
-        <v>22.45452028142319</v>
+        <v>2.564291485574031</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2874,19 +2874,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7.5</v>
+        <v>4.93</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>4.64</v>
       </c>
       <c r="E74" t="n">
-        <v>1.855668742183745</v>
+        <v>1.732801150793649</v>
       </c>
       <c r="F74" t="n">
-        <v>2.98828492777332</v>
+        <v>2.338523179624655</v>
       </c>
       <c r="G74" t="n">
-        <v>2.214499737231193</v>
+        <v>2.599145957982628</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Four-Wheel Tractor</t>
+          <t>Walking-Type Agricultural Tractor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2906,87 +2906,87 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>37.3</v>
+        <v>7.46</v>
       </c>
       <c r="D75" t="n">
-        <v>13.4</v>
+        <v>9.1</v>
       </c>
       <c r="E75" t="n">
-        <v>12.12339782106782</v>
+        <v>9.101255411255362</v>
       </c>
       <c r="F75" t="n">
-        <v>10.09853668548263</v>
+        <v>2.955263319671651</v>
       </c>
       <c r="G75" t="n">
-        <v>11.95734387965859</v>
+        <v>5.735415731065438</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hand Tractor</t>
+          <t>Water Pump</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5.97</v>
+        <v>5.22</v>
       </c>
       <c r="D76" t="n">
-        <v>1.33</v>
+        <v>0.88</v>
       </c>
       <c r="E76" t="n">
-        <v>1.88945811928812</v>
+        <v>1.763893063880563</v>
       </c>
       <c r="F76" t="n">
-        <v>2.623228377796969</v>
+        <v>2.409216713464034</v>
       </c>
       <c r="G76" t="n">
-        <v>5.852555578086171</v>
+        <v>1.708145037243689</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Water Pump</t>
+          <t>Combine Harvester</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Harvest Machinery</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>5.97</v>
+        <v>48</v>
       </c>
       <c r="D77" t="n">
-        <v>1.47</v>
+        <v>8.48</v>
       </c>
       <c r="E77" t="n">
-        <v>1.952123363812113</v>
+        <v>8.495518530543537</v>
       </c>
       <c r="F77" t="n">
-        <v>2.623228377796969</v>
+        <v>12.83773180880415</v>
       </c>
       <c r="G77" t="n">
-        <v>1.850328140095708</v>
+        <v>12.83773180880415</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>GLOBAL</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -3097,7 +3097,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -3143,13 +3143,13 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rotary Tiller</t>
+          <t>Rice Transplanter</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3163,16 +3163,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Seeder</t>
+          <t>Rotary Tiller</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3189,18 +3189,18 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sheller</t>
+          <t>Seeder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3209,125 +3209,148 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Small Engine</t>
+          <t>Sheller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stationary Engine / Irrigation</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>172</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sprayer</t>
+          <t>Small Engine</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Stationary Engine / Irrigation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thresher</t>
+          <t>Sprayer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Postharvest / Processing</t>
+          <t>Mobile Field Machinery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MACHINERY_TYPE</t>
+          <t>MACHINERY_FAMILY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Walking-Type Agricultural Tractor</t>
+          <t>Thresher</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mobile Field Machinery</t>
+          <t>Postharvest / Processing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MACHINERY_FAMILY</t>
+          <t>MACHINERY_TYPE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Walking-Type Agricultural Tractor</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mobile Field Machinery</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MACHINERY_FAMILY</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Water Pump</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Stationary Engine / Irrigation</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MACHINERY_TYPE</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>54</v>
-      </c>
-      <c r="E14" t="n">
-        <v>172</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Stationary Engine / Irrigation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MACHINERY_TYPE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
